--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DDV_HRM-2031-0440/Panel 02/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DDV_HRM-2031-0440/Panel 02/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.80134</v>
+        <v>16.77755</v>
       </c>
       <c r="D2" t="n">
-        <v>16.39222</v>
+        <v>16.32784</v>
       </c>
       <c r="E2" t="n">
-        <v>16.5464</v>
+        <v>16.54531</v>
       </c>
       <c r="F2" t="n">
-        <v>42.78566</v>
+        <v>42.11374</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05065</v>
+        <v>0.05093</v>
       </c>
       <c r="H2" t="n">
-        <v>1.82451</v>
+        <v>1.81427</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.80274</v>
+        <v>17.04752</v>
       </c>
       <c r="D3" t="n">
-        <v>16.4884</v>
+        <v>16.54174</v>
       </c>
       <c r="E3" t="n">
-        <v>16.84299</v>
+        <v>16.60798</v>
       </c>
       <c r="F3" t="n">
-        <v>42.93462</v>
+        <v>42.92874</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04998</v>
+        <v>0.04978</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80114</v>
+        <v>1.80054</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.17153</v>
+        <v>17.15053</v>
       </c>
       <c r="D4" t="n">
-        <v>16.81643</v>
+        <v>16.80063</v>
       </c>
       <c r="E4" t="n">
-        <v>16.76536</v>
+        <v>16.86371</v>
       </c>
       <c r="F4" t="n">
-        <v>42.54606</v>
+        <v>42.7222</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0504</v>
+        <v>0.04838</v>
       </c>
       <c r="H4" t="n">
-        <v>1.84337</v>
+        <v>1.83175</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.45832</v>
+        <v>17.07945</v>
       </c>
       <c r="D6" t="n">
-        <v>15.84912</v>
+        <v>15.92513</v>
       </c>
       <c r="E6" t="n">
-        <v>16.27662</v>
+        <v>16.57424</v>
       </c>
       <c r="F6" t="n">
-        <v>22.04953</v>
+        <v>21.3682</v>
       </c>
       <c r="G6" t="n">
-        <v>33.85135</v>
+        <v>33.89388</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.53555</v>
+        <v>17.0094</v>
       </c>
       <c r="D7" t="n">
-        <v>15.77171</v>
+        <v>15.95306</v>
       </c>
       <c r="E7" t="n">
-        <v>16.1977</v>
+        <v>16.54812</v>
       </c>
       <c r="F7" t="n">
-        <v>21.79245</v>
+        <v>21.69791</v>
       </c>
       <c r="G7" t="n">
-        <v>34.41828</v>
+        <v>34.89127</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.69936</v>
+        <v>16.70426</v>
       </c>
       <c r="D8" t="n">
-        <v>15.853</v>
+        <v>16.44021</v>
       </c>
       <c r="E8" t="n">
-        <v>16.2689</v>
+        <v>16.68106</v>
       </c>
       <c r="F8" t="n">
-        <v>21.63624</v>
+        <v>21.33568</v>
       </c>
       <c r="G8" t="n">
-        <v>34.27198</v>
+        <v>34.51685</v>
       </c>
     </row>
   </sheetData>
